--- a/outputs/evaluation/decision/v1/CF_M05/run_1/CF_M05_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_1/CF_M05_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5</v>
+        <v>0.8889</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2727</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8979</v>
+        <v>0.9098000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0833</v>
+        <v>0.2938</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.9085</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5</v>
+        <v>0.8889</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2727</v>
+        <v>0.6153999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -752,34 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
         <v>6</v>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,28 +974,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8601</v>
+        <v>0.8344</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1015,69 +1015,69 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.8605</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>This structure allows to develop, deploy and scale each service autonomously, facilitating maintenance, flexibility and the evolution of the system.</t>
+          <t>This component is responsible for verifying the identity of users through authentication mechanisms, determines the permissions associated with each user or service according to defined roles and policies as well as the groups to which it belongs and manages the creation and maintenance of these roles. This microservice is essential to maintain the confidentiality and protection of data.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_07, R_45</t>
+          <t>R_48, Security</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
+          <t>*CF_M05_C11</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M05_AD06</t>
+          <t>CF_M05_AD01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9111</v>
+        <v>0.86</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1088,59 +1088,57 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The use of this type of architecture allows high scalability, availability and accessibility, as the management of resources can be done according to needs and anywhere with an Internet connection.</t>
+          <t>This structure allows to develop, deploy, and scale each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Cloud computing, R_43, R_44</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AU_17, AU_18, AU_19</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
+          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M05_P05</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -1151,81 +1149,510 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>CF_M05_AD03</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8648</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8804</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>This component incorporates the binaries necessary for the frontEnd both of the portal itself and of the rest of the portal applications. This ensures that the presentation layer is available and updated, facilitating deployment and reducing dependence on external elements. In this way, the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C_01, R_33, R_34</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>CF_M05_C01, *CF_M05_C12</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CF_M05_AU02</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8673</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated. This structure clarifies roles, avoids unnecessary coupling, and facilitates testing, reusing, and maintaining the code over time.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>CF_M05_AD08</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0.9226</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C6" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C_05, Security, Integrity</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CF_M05_AD02</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9394</v>
+      </c>
+      <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.7994</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications. Specifically, it blocks any unauthorized connection attempt and applies certain security protocols to prevent improper access and possible vulnerabilities.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>R_48, Security</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>CF_M05_C09 , *CF_M05_C11</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9921</v>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity and persistence.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>CF_M05_P02</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>61</v>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>The use of this architecture allows high scalability, availability, and accessibility, since the management of resources can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by the resource providers, and without large expenses, due to the fact that one pays for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>C_06, C_07, Availability, Scalability</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>AU_17, AU_18, AU_19</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CF_M05_AD05</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.9106</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>This component acts as a traceability and auditing mechanism, ensuring that each interaction is documented for subsequent analysis, incident resolution, and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>C_09</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>*CF_M05_C13</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU04</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1239,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,7 +1709,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1292,7 +1719,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_02, C_04</t>
+          <t>C_02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1312,76 +1739,6 @@
       </c>
       <c r="G2" t="n">
         <v>0.6768999999999999</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C_09</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CF_M05_AD08</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.7171</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AWS is a consolidated cloud platform with robust services and a reliable infrastructure. [...] Another reason why AWS was chosen was that this platform invests heavily in security and certifications, manages multiple levels of security and offers tools to protect data and infrastructures facilitating compliance with legal regulations and international standards.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Security, Certifications</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CF_M05_AD02</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.6828</v>
       </c>
     </row>
   </sheetData>
@@ -1395,7 +1752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1438,265 +1795,166 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AD02</t>
+          <t>CF_M05_AD07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M05_C09 , *CF_M05_C11</t>
+          <t>*CF_M05_C15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M05_AU01</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6828</v>
+        <v>0.8676</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD03</t>
+          <t>CF_M05_AD09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CF_M05_C01, *CF_M05_C12</t>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6876</v>
+        <v>0.7177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C11</t>
+          <t>*CF_M05_C14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_09</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6751</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>CF_M05_C06, CF_M05_C07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6413</v>
+        <v>0.7586000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>*CF_M05_C18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8672</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CF_M05_AD09</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU30</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>76</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.7235</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CF_M05_AD10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>*CF_M05_C14</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>77</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0.6768999999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CF_M05_AD11</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU07</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>81</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7635</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/decision/v1/CF_M05/run_1/CF_M05_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_1/CF_M05_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8889</v>
+        <v>0.1538</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.1538</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.7771</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2938</v>
+        <v>0.1667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9085</v>
+        <v>0.9402</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8889</v>
+        <v>0.1538</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.1538</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,31 +755,31 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -792,31 +792,31 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,28 +974,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD03</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8344</v>
+        <v>0.7706</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1015,51 +1015,51 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8605</v>
+        <v>0.8804</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>This component is responsible for verifying the identity of users through authentication mechanisms, determines the permissions associated with each user or service according to defined roles and policies as well as the groups to which it belongs and manages the creation and maintenance of these roles. This microservice is essential to maintain the confidentiality and protection of data.</t>
+          <t>El microservei del portal té com a funció principal oferir una interfície centralitzada per a l’accés a les diferents aplicacions de VWGS.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R_48, Security</t>
+          <t>AU_09, C_01</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M05_C11</t>
+          <t>CF_M05_C01, *CF_M05_C12</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.86</v>
+        <v>0.7836</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>This structure allows to develop, deploy, and scale each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
+          <t>Com ja s’ha pogut anar intuint en apartats anteriors, l’aplicació té una arquitectura basada en microserveis. Consisteix a dividir el sistema en un conjunt de serveis petits, independents i autònoms on cada microservei s’encarrega d’una funcionalitat específica i es comunica amb la resta mitjançant diversos sistemes de missatgeria.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>P_02, C_06</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1139,520 +1139,6 @@
       </c>
       <c r="U3" t="n">
         <v>56</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CF_M05_AD03</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.8648</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.8804</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>This component incorporates the binaries necessary for the frontEnd both of the portal itself and of the rest of the portal applications. This ensures that the presentation layer is available and updated, facilitating deployment and reducing dependence on external elements. In this way, the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>C_01, R_33, R_34</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>CF_M05_C01, *CF_M05_C12</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_09</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CF_M05_AD12</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.8673</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated. This structure clarifies roles, avoids unnecessary coupling, and facilitates testing, reusing, and maintaining the code over time.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>*CF_M05_C14</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CF_M05_AD08</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9245</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>C_05, Security, Integrity</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CF_M05_P02</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CF_M05_AD02</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.9394</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.7994</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications. Specifically, it blocks any unauthorized connection attempt and applies certain security protocols to prevent improper access and possible vulnerabilities.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>R_48, Security</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>CF_M05_C09 , *CF_M05_C11</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CF_M05_AD06</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.9921</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>The use of this architecture allows high scalability, availability, and accessibility, since the management of resources can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by the resource providers, and without large expenses, due to the fact that one pays for the resources consumed.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>C_06, C_07, Availability, Scalability</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>AU_17, AU_18, AU_19</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>CF_M05_P05</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CF_M05_AD05</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9956</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.9106</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>This component acts as a traceability and auditing mechanism, ensuring that each interaction is documented for subsequent analysis, incident resolution, and regulatory compliance.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>C_09</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>*CF_M05_C13</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU04</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1666,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,36 +1195,386 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aquest microservei té com a funció principal l’encaminament de totes les comunicacions cap al microservei corresponent dins de l’arquitectura del sistema.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AU_08, C_05</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CF_M05_AD04</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6762</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A més de la seva funció com a portal, aquest microservei incorpora els binaris necessaris per al frontEnd tant del mateix portal com de la resta d’aplicacions del portal.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AU_09, C_01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CF_M05_AD03</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7266</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>El microservei Access Control té com a objectiu principal la gestió d’autenticació d’usuaris i els seus permisos dins de l’aplicació.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AU_10, R_48</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M05_AD04</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6817</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>El microservei Communication Log té com a finalitat principal registrar totes les comunicacions que es produeixen dins del sistema, tant entre microserveis com amb serveis externs.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AU_11, C_09</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD05</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Té com a funció principal la planificació i programació de processos dins del sistema.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AU_12, C_06</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CF_M05_AD08</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6084000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>En el present projecte, el client s’ha desenvolupat amb Angular, implementant una Single-PageApplication (SPA) que renderitza vistes dinàmiques i gestiona la navegació interna sense haver de recarregar la pàgina, millorant la fluïdesa d’ús.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AU_13, P_03, C_02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AU_13, P_03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>61, 62</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CF_M05_AD09</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7027</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>AD_08</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>C_02</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pel servidor s’ha utilitzat Spring Boot, que proporciona una plataforma per exposar una API REST.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AU_14, P_04, C_05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AU_14, P_04</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CF_M05_AD10</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.6768999999999999</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6495</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>El protocol d’intercanvi de missatges que es fa servir en aquest cas és HTTP i el format de dades emprat és JSON.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AU_15, C_05</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6165</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AD_10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>El proveïdor per aquest projecte és Amazon Web Services el qual té un ampli catàleg de serveis i recursos cloud.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AU_17, C_06</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6708</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AD_11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pel desplegament de l’aplicació s’ha fet ús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s), una plataforma d’orquestració de contenidors creada per Google, sense necessitat d’instal·lar-la ni mantenir-la.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AU_18, AU_19, C_06</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AU_18, AU_19</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6858</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AD_12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P_01, C_05</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CF_M05_AD08</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6850000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1752,7 +1588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,166 +1631,364 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>CF_M05_C09 , *CF_M05_C11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU01</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8676</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>*CF_M05_C11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7177</v>
+        <v>0.6817</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C14</t>
+          <t>*CF_M05_C13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_09</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7083</v>
+        <v>0.7118</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD11</t>
+          <t>CF_M05_AD06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_P05</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_11</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.6858</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>CF_M05_AD07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>*CF_M05_C15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>61</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AD_12</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.681</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CF_M05_AD08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AD_12</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CF_M05_AD09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>76</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7027</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M05_AD10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6516999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AD_11</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6851</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>78</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AD_13</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6586</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>CF_M05_AD13</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>*CF_M05_C18</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E12" t="n">
         <v>82</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.7635</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.636</v>
       </c>
     </row>
   </sheetData>
